--- a/data/ENPRA (TRY).xlsx
+++ b/data/ENPRA (TRY).xlsx
@@ -403,13 +403,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:F57"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -417,15 +418,18 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
     </row>
@@ -439,15 +443,18 @@
         <v xml:space="preserve">    FİNANSAL VARLIKLAR (Net)</v>
       </c>
       <c r="B3">
+        <v>108359000000</v>
+      </c>
+      <c r="C3">
         <v>106668720000</v>
       </c>
-      <c r="C3">
-        <v>91883452000</v>
-      </c>
       <c r="D3">
+        <v>91883000000</v>
+      </c>
+      <c r="E3">
         <v>73395086000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>7923749000</v>
       </c>
     </row>
@@ -456,15 +463,18 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B4">
+        <v>84204000000</v>
+      </c>
+      <c r="C4">
         <v>87645307000</v>
       </c>
-      <c r="C4">
-        <v>76811174000</v>
-      </c>
       <c r="D4">
+        <v>76811000000</v>
+      </c>
+      <c r="E4">
         <v>61014972000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>7923749000</v>
       </c>
     </row>
@@ -484,21 +494,27 @@
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıklar</v>
       </c>
       <c r="B6">
+        <v>24154000000</v>
+      </c>
+      <c r="C6">
         <v>18314843000</v>
       </c>
-      <c r="C6">
-        <v>13937347000</v>
-      </c>
       <c r="D6">
+        <v>13937000000</v>
+      </c>
+      <c r="E6">
         <v>11984636000</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0</v>
       </c>
     </row>
@@ -507,15 +523,18 @@
         <v xml:space="preserve">    İtfa Edilmiş Maliyeti ile Ölçülen Finansal Varlıklar</v>
       </c>
       <c r="B7">
+        <v>16158000000</v>
+      </c>
+      <c r="C7">
         <v>15493111000</v>
       </c>
-      <c r="C7">
-        <v>8612018000</v>
-      </c>
       <c r="D7">
+        <v>8612000000</v>
+      </c>
+      <c r="E7">
         <v>8337286000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0</v>
       </c>
     </row>
@@ -524,15 +543,18 @@
         <v xml:space="preserve">    Türev Finansal Varlıklar</v>
       </c>
       <c r="B8">
+        <v>1000000</v>
+      </c>
+      <c r="C8">
         <v>708570000</v>
       </c>
-      <c r="C8">
-        <v>1134931000</v>
-      </c>
       <c r="D8">
+        <v>1135000000</v>
+      </c>
+      <c r="E8">
         <v>395478000</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
@@ -551,15 +573,18 @@
         <v xml:space="preserve">    KREDİLER (Net)</v>
       </c>
       <c r="B11">
+        <v>181654000000</v>
+      </c>
+      <c r="C11">
         <v>167641703000</v>
       </c>
-      <c r="C11">
-        <v>152901192000</v>
-      </c>
       <c r="D11">
+        <v>152901000000</v>
+      </c>
+      <c r="E11">
         <v>141428640000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0</v>
       </c>
     </row>
@@ -568,15 +593,18 @@
         <v xml:space="preserve">    Krediler</v>
       </c>
       <c r="B12">
+        <v>176529000000</v>
+      </c>
+      <c r="C12">
         <v>163812310000</v>
       </c>
-      <c r="C12">
-        <v>154735718000</v>
-      </c>
       <c r="D12">
+        <v>154736000000</v>
+      </c>
+      <c r="E12">
         <v>141939867000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0</v>
       </c>
     </row>
@@ -596,6 +624,9 @@
       <c r="E13">
         <v>0</v>
       </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -613,6 +644,9 @@
       <c r="E14">
         <v>0</v>
       </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -624,15 +658,18 @@
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
       <c r="B16">
+        <v>-11033000000</v>
+      </c>
+      <c r="C16">
         <v>-11663718000</v>
       </c>
-      <c r="C16">
-        <v>-10446544000</v>
-      </c>
       <c r="D16">
+        <v>-10447000000</v>
+      </c>
+      <c r="E16">
         <v>-8848513000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0</v>
       </c>
     </row>
@@ -652,6 +689,9 @@
       <c r="E17">
         <v>0</v>
       </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -669,6 +709,9 @@
       <c r="E18">
         <v>0</v>
       </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -686,6 +729,9 @@
       <c r="E19">
         <v>0</v>
       </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -703,6 +749,9 @@
       <c r="E20">
         <v>0</v>
       </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -720,21 +769,27 @@
       <c r="E21">
         <v>0</v>
       </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    MADDİ DURAN VARLIKLAR (Net)</v>
       </c>
       <c r="B22">
+        <v>1502000000</v>
+      </c>
+      <c r="C22">
         <v>1620484000</v>
       </c>
-      <c r="C22">
-        <v>1720620000</v>
-      </c>
       <c r="D22">
+        <v>1721000000</v>
+      </c>
+      <c r="E22">
         <v>1372636000</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>1429055000</v>
       </c>
     </row>
@@ -743,15 +798,18 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar (Net)</v>
       </c>
       <c r="B23">
+        <v>1465000000</v>
+      </c>
+      <c r="C23">
         <v>1234778000</v>
       </c>
-      <c r="C23">
-        <v>988440000</v>
-      </c>
       <c r="D23">
+        <v>988000000</v>
+      </c>
+      <c r="E23">
         <v>783606000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>107159000</v>
       </c>
     </row>
@@ -771,6 +829,9 @@
       <c r="E24">
         <v>0</v>
       </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -780,12 +841,15 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>23021000</v>
+        <v>0</v>
       </c>
       <c r="D25">
+        <v>23000000</v>
+      </c>
+      <c r="E25">
         <v>323309000</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>2574000</v>
       </c>
     </row>
@@ -794,15 +858,18 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B26">
+        <v>1697000000</v>
+      </c>
+      <c r="C26">
         <v>1183307000</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
       <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>330281000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0</v>
       </c>
     </row>
@@ -811,15 +878,18 @@
         <v xml:space="preserve">    Diğer Aktifler</v>
       </c>
       <c r="B27">
+        <v>7114000000</v>
+      </c>
+      <c r="C27">
         <v>5999077000</v>
       </c>
-      <c r="C27">
-        <v>2631651000</v>
-      </c>
       <c r="D27">
+        <v>2632000000</v>
+      </c>
+      <c r="E27">
         <v>2764809000</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>231676000</v>
       </c>
     </row>
@@ -828,15 +898,18 @@
         <v xml:space="preserve">    VARLIKLAR TOPLAMI</v>
       </c>
       <c r="B28">
+        <v>301791000000</v>
+      </c>
+      <c r="C28">
         <v>284348069000</v>
       </c>
-      <c r="C28">
-        <v>250148376000</v>
-      </c>
       <c r="D28">
+        <v>250148000000</v>
+      </c>
+      <c r="E28">
         <v>220398367000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>9694213000</v>
       </c>
     </row>
@@ -845,15 +918,18 @@
         <v xml:space="preserve">    Mevduat</v>
       </c>
       <c r="B29">
+        <v>231921000000</v>
+      </c>
+      <c r="C29">
         <v>223762771000</v>
       </c>
-      <c r="C29">
-        <v>205482962000</v>
-      </c>
       <c r="D29">
+        <v>205483000000</v>
+      </c>
+      <c r="E29">
         <v>196815464000</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0</v>
       </c>
     </row>
@@ -878,21 +954,27 @@
       <c r="E31">
         <v>0</v>
       </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Para Piyasasına Borçlar</v>
       </c>
       <c r="B32">
+        <v>25028000000</v>
+      </c>
+      <c r="C32">
         <v>20021918000</v>
       </c>
-      <c r="C32">
-        <v>9887761000</v>
-      </c>
       <c r="D32">
-        <v>0</v>
+        <v>9888000000</v>
       </c>
       <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <v>0</v>
       </c>
     </row>
@@ -912,6 +994,9 @@
       <c r="E33">
         <v>0</v>
       </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -929,6 +1014,9 @@
       <c r="E34">
         <v>0</v>
       </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -946,6 +1034,9 @@
       <c r="E35">
         <v>0</v>
       </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -963,6 +1054,9 @@
       <c r="E36">
         <v>0</v>
       </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -980,6 +1074,9 @@
       <c r="E37">
         <v>0</v>
       </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -997,21 +1094,27 @@
       <c r="E38">
         <v>0</v>
       </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
         <v xml:space="preserve">    Türev Finansal Yükümlülükler</v>
       </c>
       <c r="B39">
+        <v>4364000000</v>
+      </c>
+      <c r="C39">
         <v>3758629000</v>
       </c>
-      <c r="C39">
-        <v>434880000</v>
-      </c>
       <c r="D39">
+        <v>435000000</v>
+      </c>
+      <c r="E39">
         <v>39000</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0</v>
       </c>
     </row>
@@ -1031,21 +1134,27 @@
       <c r="E40">
         <v>0</v>
       </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Yükümlülükler</v>
       </c>
       <c r="B41">
+        <v>272000000</v>
+      </c>
+      <c r="C41">
         <v>253822000</v>
       </c>
-      <c r="C41">
-        <v>245875000</v>
-      </c>
       <c r="D41">
+        <v>245000000</v>
+      </c>
+      <c r="E41">
         <v>60419000</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>3114000</v>
       </c>
     </row>
@@ -1054,15 +1163,18 @@
         <v xml:space="preserve">    Karşılıklar</v>
       </c>
       <c r="B42">
+        <v>701000000</v>
+      </c>
+      <c r="C42">
         <v>588824000</v>
       </c>
-      <c r="C42">
-        <v>621743000</v>
-      </c>
       <c r="D42">
+        <v>622000000</v>
+      </c>
+      <c r="E42">
         <v>526967000</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>13799000</v>
       </c>
     </row>
@@ -1071,15 +1183,18 @@
         <v xml:space="preserve">    Cari Vergi Borcu</v>
       </c>
       <c r="B43">
+        <v>1233000000</v>
+      </c>
+      <c r="C43">
         <v>1981023000</v>
       </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
         <v>0</v>
       </c>
     </row>
@@ -1091,12 +1206,15 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>184281000</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>184000000</v>
       </c>
       <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
         <v>37759000</v>
       </c>
     </row>
@@ -1116,6 +1234,9 @@
       <c r="E45">
         <v>0</v>
       </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1133,21 +1254,27 @@
       <c r="E46">
         <v>0</v>
       </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Diğer Yükümlülükler</v>
       </c>
       <c r="B47">
+        <v>15647000000</v>
+      </c>
+      <c r="C47">
         <v>13408676000</v>
       </c>
-      <c r="C47">
-        <v>14380506000</v>
-      </c>
       <c r="D47">
+        <v>14381000000</v>
+      </c>
+      <c r="E47">
         <v>6092250000</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>439856000</v>
       </c>
     </row>
@@ -1156,15 +1283,18 @@
         <v xml:space="preserve">    ÖZKAYNAKLAR</v>
       </c>
       <c r="B48">
+        <v>22625000000</v>
+      </c>
+      <c r="C48">
         <v>20572406000</v>
       </c>
-      <c r="C48">
-        <v>18910368000</v>
-      </c>
       <c r="D48">
+        <v>18910000000</v>
+      </c>
+      <c r="E48">
         <v>16903228000</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>9199685000</v>
       </c>
     </row>
@@ -1173,15 +1303,18 @@
         <v xml:space="preserve">    Ödenmiş Sermaye</v>
       </c>
       <c r="B49">
-        <v>12475290000</v>
+        <v>12475000000</v>
       </c>
       <c r="C49">
         <v>12475290000</v>
       </c>
       <c r="D49">
+        <v>12475000000</v>
+      </c>
+      <c r="E49">
         <v>12475290000</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>8684430000</v>
       </c>
     </row>
@@ -1190,15 +1323,18 @@
         <v xml:space="preserve">    Sermaye Yedekleri</v>
       </c>
       <c r="B50">
-        <v>290340000</v>
+        <v>290000000</v>
       </c>
       <c r="C50">
         <v>290340000</v>
       </c>
       <c r="D50">
+        <v>290000000</v>
+      </c>
+      <c r="E50">
         <v>295283000</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0</v>
       </c>
     </row>
@@ -1207,15 +1343,18 @@
         <v xml:space="preserve">    Kâr veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler veya Giderler</v>
       </c>
       <c r="B51">
-        <v>-21158000</v>
+        <v>-21000000</v>
       </c>
       <c r="C51">
         <v>-21158000</v>
       </c>
       <c r="D51">
+        <v>-21000000</v>
+      </c>
+      <c r="E51">
         <v>-103000</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>-103000</v>
       </c>
     </row>
@@ -1224,15 +1363,18 @@
         <v xml:space="preserve">    Kâr veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler veya Giderler</v>
       </c>
       <c r="B52">
+        <v>-158000000</v>
+      </c>
+      <c r="C52">
         <v>-264461000</v>
       </c>
-      <c r="C52">
-        <v>-5399000</v>
-      </c>
       <c r="D52">
+        <v>-5000000</v>
+      </c>
+      <c r="E52">
         <v>-310849000</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0</v>
       </c>
     </row>
@@ -1241,15 +1383,18 @@
         <v xml:space="preserve">    Kar Yedekleri</v>
       </c>
       <c r="B53">
+        <v>6171000000</v>
+      </c>
+      <c r="C53">
         <v>6171295000</v>
       </c>
-      <c r="C53">
+      <c r="D53">
+        <v>33000000</v>
+      </c>
+      <c r="E53">
         <v>33423000</v>
       </c>
-      <c r="D53">
-        <v>33423000</v>
-      </c>
-      <c r="E53">
+      <c r="F53">
         <v>0</v>
       </c>
     </row>
@@ -1258,15 +1403,18 @@
         <v xml:space="preserve">    Kar veya Zarar</v>
       </c>
       <c r="B54">
+        <v>3868000000</v>
+      </c>
+      <c r="C54">
         <v>1921100000</v>
       </c>
-      <c r="C54">
-        <v>6137872000</v>
-      </c>
       <c r="D54">
+        <v>6138000000</v>
+      </c>
+      <c r="E54">
         <v>4410184000</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>515358000</v>
       </c>
     </row>
@@ -1278,12 +1426,15 @@
         <v>0</v>
       </c>
       <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>482000000</v>
+      </c>
+      <c r="E55">
         <v>481935000</v>
       </c>
-      <c r="D55">
-        <v>481935000</v>
-      </c>
-      <c r="E55">
+      <c r="F55">
         <v>-153097000</v>
       </c>
     </row>
@@ -1292,15 +1443,18 @@
         <v xml:space="preserve">    Dönem Net Kâr veya Zararı</v>
       </c>
       <c r="B56">
+        <v>3868000000</v>
+      </c>
+      <c r="C56">
         <v>1921100000</v>
       </c>
-      <c r="C56">
-        <v>5655937000</v>
-      </c>
       <c r="D56">
+        <v>5656000000</v>
+      </c>
+      <c r="E56">
         <v>3928249000</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>668455000</v>
       </c>
     </row>
@@ -1309,28 +1463,31 @@
         <v xml:space="preserve">    YÜKÜMLÜLÜKLER TOPLAMI</v>
       </c>
       <c r="B57">
+        <v>301791000000</v>
+      </c>
+      <c r="C57">
         <v>284348069000</v>
       </c>
-      <c r="C57">
-        <v>250148376000</v>
-      </c>
       <c r="D57">
+        <v>250148000000</v>
+      </c>
+      <c r="E57">
         <v>220398367000</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>9694213000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F57"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:I46"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1339,6 +1496,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1346,21 +1505,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
     </row>
@@ -1374,21 +1539,27 @@
         <v xml:space="preserve">    FAİZ GELİRLERİ</v>
       </c>
       <c r="B3">
-        <v>17036957000</v>
+        <v>36469000000</v>
       </c>
       <c r="C3">
+        <v>17036000000</v>
+      </c>
+      <c r="D3">
         <v>26460324000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>8957834000</v>
       </c>
-      <c r="E3">
-        <v>794703000</v>
-      </c>
       <c r="F3">
+        <v>1746000000</v>
+      </c>
+      <c r="G3">
+        <v>795000000</v>
+      </c>
+      <c r="H3">
         <v>296810000</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>200857000</v>
       </c>
     </row>
@@ -1402,21 +1573,27 @@
         <v xml:space="preserve">    Kredilerden Alınan Faizler</v>
       </c>
       <c r="B5">
-        <v>12545292000</v>
+        <v>26316000000</v>
       </c>
       <c r="C5">
+        <v>12545000000</v>
+      </c>
+      <c r="D5">
         <v>16749230000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>4447673000</v>
       </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
     </row>
@@ -1425,21 +1602,27 @@
         <v xml:space="preserve">    Zorunlu Karşılıklardan Alınan Faizler</v>
       </c>
       <c r="B6">
-        <v>2275479000</v>
+        <v>4889000000</v>
       </c>
       <c r="C6">
+        <v>2276000000</v>
+      </c>
+      <c r="D6">
         <v>3022148000</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>882627000</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
     </row>
@@ -1448,21 +1631,27 @@
         <v xml:space="preserve">    Bankalardan Alınan Faizler</v>
       </c>
       <c r="B7">
-        <v>201341000</v>
+        <v>454000000</v>
       </c>
       <c r="C7">
+        <v>201000000</v>
+      </c>
+      <c r="D7">
         <v>2139144000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1352344000</v>
       </c>
-      <c r="E7">
-        <v>310716000</v>
-      </c>
       <c r="F7">
+        <v>325000000</v>
+      </c>
+      <c r="G7">
+        <v>311000000</v>
+      </c>
+      <c r="H7">
         <v>181219000</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>85266000</v>
       </c>
     </row>
@@ -1471,21 +1660,27 @@
         <v xml:space="preserve">    Para Piyasası İşlemlerinden Alınan Faizler</v>
       </c>
       <c r="B8">
-        <v>164000</v>
+        <v>8000000</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>2089000000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1671159000</v>
       </c>
-      <c r="E8">
-        <v>482897000</v>
-      </c>
       <c r="F8">
+        <v>1408000000</v>
+      </c>
+      <c r="G8">
+        <v>483000000</v>
+      </c>
+      <c r="H8">
         <v>115591000</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>115591000</v>
       </c>
     </row>
@@ -1494,21 +1689,27 @@
         <v xml:space="preserve">    Menkul Değerlerden Alınan Faizler</v>
       </c>
       <c r="B9">
-        <v>2011240000</v>
+        <v>4799000000</v>
       </c>
       <c r="C9">
+        <v>2011000000</v>
+      </c>
+      <c r="D9">
         <v>2460786000</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>604031000</v>
       </c>
-      <c r="E9">
-        <v>1089000</v>
-      </c>
       <c r="F9">
-        <v>0</v>
+        <v>13000000</v>
       </c>
       <c r="G9">
+        <v>1000000</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
     </row>
@@ -1534,20 +1735,26 @@
       <c r="G10">
         <v>0</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Diğer Faiz Gelirleri</v>
       </c>
       <c r="B11">
-        <v>3441000</v>
+        <v>3000000</v>
       </c>
       <c r="C11">
+        <v>3000000</v>
+      </c>
+      <c r="D11">
         <v>16000</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
       <c r="E11">
         <v>0</v>
       </c>
@@ -1555,6 +1762,12 @@
         <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>0</v>
       </c>
     </row>
@@ -1563,21 +1776,27 @@
         <v xml:space="preserve">    FAİZ GİDERLERİ (-)</v>
       </c>
       <c r="B12">
-        <v>-11726606000</v>
+        <v>-25669000000</v>
       </c>
       <c r="C12">
+        <v>-11727000000</v>
+      </c>
+      <c r="D12">
         <v>-16684686000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-4627216000</v>
       </c>
-      <c r="E12">
-        <v>-6136000</v>
-      </c>
       <c r="F12">
+        <v>-16000000</v>
+      </c>
+      <c r="G12">
+        <v>-6000000</v>
+      </c>
+      <c r="H12">
         <v>-4134000</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>-3900000</v>
       </c>
     </row>
@@ -1591,21 +1810,27 @@
         <v xml:space="preserve">    Mevduata Verilen Faizler</v>
       </c>
       <c r="B14">
-        <v>-11395885000</v>
+        <v>-24792000000</v>
       </c>
       <c r="C14">
+        <v>-11396000000</v>
+      </c>
+      <c r="D14">
         <v>-16524396000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>-4608337000</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
       <c r="F14">
-        <v>0</v>
+        <v>-1000000</v>
       </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>0</v>
       </c>
     </row>
@@ -1614,21 +1839,27 @@
         <v xml:space="preserve">    Kullanılan Kredilere Verilen Faizler</v>
       </c>
       <c r="B15">
-        <v>-973000</v>
+        <v>-1000000</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>-1000000</v>
       </c>
       <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>-562000</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>-3000</v>
       </c>
     </row>
@@ -1637,21 +1868,27 @@
         <v xml:space="preserve">    Para Piyasası İşlemlerine Verilen Faizler</v>
       </c>
       <c r="B16">
-        <v>-292721000</v>
+        <v>-792000000</v>
       </c>
       <c r="C16">
+        <v>-293000000</v>
+      </c>
+      <c r="D16">
         <v>-110082000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-4000</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>0</v>
       </c>
     </row>
@@ -1677,27 +1914,39 @@
       <c r="G17">
         <v>0</v>
       </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faiz Giderleri</v>
       </c>
       <c r="B18">
-        <v>-7348000</v>
+        <v>-30000000</v>
       </c>
       <c r="C18">
+        <v>-7000000</v>
+      </c>
+      <c r="D18">
         <v>-24870000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>-12859000</v>
       </c>
-      <c r="E18">
-        <v>-4125000</v>
-      </c>
       <c r="F18">
+        <v>-11000000</v>
+      </c>
+      <c r="G18">
+        <v>-4000000</v>
+      </c>
+      <c r="H18">
         <v>-3525000</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>-3525000</v>
       </c>
     </row>
@@ -1706,21 +1955,27 @@
         <v xml:space="preserve">    NET FAİZ GELİRİ VEYA GİDERİ</v>
       </c>
       <c r="B19">
-        <v>5310351000</v>
+        <v>10800000000</v>
       </c>
       <c r="C19">
+        <v>5309000000</v>
+      </c>
+      <c r="D19">
         <v>9775638000</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>4330618000</v>
       </c>
-      <c r="E19">
-        <v>788567000</v>
-      </c>
       <c r="F19">
+        <v>1730000000</v>
+      </c>
+      <c r="G19">
+        <v>789000000</v>
+      </c>
+      <c r="H19">
         <v>292676000</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>196957000</v>
       </c>
     </row>
@@ -1734,21 +1989,27 @@
         <v xml:space="preserve">    NET ÜCRET VE KOMİSYON GELİRLERİ VEYA GİDERLERİ</v>
       </c>
       <c r="B21">
-        <v>2490378000</v>
+        <v>5466000000</v>
       </c>
       <c r="C21">
+        <v>2490000000</v>
+      </c>
+      <c r="D21">
         <v>3667938000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1115568000</v>
       </c>
-      <c r="E21">
-        <v>-646000</v>
-      </c>
       <c r="F21">
+        <v>-2000000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>-724000</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>0</v>
       </c>
     </row>
@@ -1757,21 +2018,27 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B22">
-        <v>3909076000</v>
+        <v>8430000000</v>
       </c>
       <c r="C22">
+        <v>3909000000</v>
+      </c>
+      <c r="D22">
         <v>5563591000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>1459666000</v>
       </c>
-      <c r="E22">
-        <v>1000</v>
-      </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>0</v>
       </c>
     </row>
@@ -1780,21 +2047,27 @@
         <v xml:space="preserve">    Verilen Ücret ve Komisyonlar (-)</v>
       </c>
       <c r="B23">
-        <v>-1418698000</v>
+        <v>-2964000000</v>
       </c>
       <c r="C23">
+        <v>-1419000000</v>
+      </c>
+      <c r="D23">
         <v>-1895653000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-344098000</v>
       </c>
-      <c r="E23">
-        <v>-647000</v>
-      </c>
       <c r="F23">
+        <v>-2000000</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>-724000</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>0</v>
       </c>
     </row>
@@ -1803,21 +2076,27 @@
         <v xml:space="preserve">    PERSONEL GİDERLERİ (-)</v>
       </c>
       <c r="B24">
-        <v>-910352000</v>
+        <v>-1866000000</v>
       </c>
       <c r="C24">
+        <v>-910000000</v>
+      </c>
+      <c r="D24">
         <v>-1070172000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>-386316000</v>
       </c>
-      <c r="E24">
-        <v>-43826000</v>
-      </c>
       <c r="F24">
+        <v>-100000000</v>
+      </c>
+      <c r="G24">
+        <v>-44000000</v>
+      </c>
+      <c r="H24">
         <v>-65830000</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>-41031000</v>
       </c>
     </row>
@@ -1843,27 +2122,39 @@
       <c r="G25">
         <v>0</v>
       </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    TİCARİ KAR VEYA ZARAR (Net)</v>
       </c>
       <c r="B26">
-        <v>-611413000</v>
+        <v>-1264000000</v>
       </c>
       <c r="C26">
+        <v>-611000000</v>
+      </c>
+      <c r="D26">
         <v>-1689837000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>-636078000</v>
       </c>
-      <c r="E26">
-        <v>48397000</v>
-      </c>
       <c r="F26">
+        <v>91000000</v>
+      </c>
+      <c r="G26">
+        <v>48000000</v>
+      </c>
+      <c r="H26">
         <v>1395480000</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>1131705000</v>
       </c>
     </row>
@@ -1872,21 +2163,27 @@
         <v xml:space="preserve">    Sermaye Piyasası İşlemleri Karı (Zararı)</v>
       </c>
       <c r="B27">
-        <v>-13419000</v>
+        <v>-13000000</v>
       </c>
       <c r="C27">
+        <v>-13000000</v>
+      </c>
+      <c r="D27">
         <v>-57074000</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>675000</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>0</v>
       </c>
     </row>
@@ -1895,21 +2192,27 @@
         <v xml:space="preserve">    Türev Finansal İşlemlerden Kar (Zarar)</v>
       </c>
       <c r="B28">
-        <v>-1047788000</v>
+        <v>-2015000000</v>
       </c>
       <c r="C28">
+        <v>-1048000000</v>
+      </c>
+      <c r="D28">
         <v>84901000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-448863000</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>0</v>
       </c>
     </row>
@@ -1918,21 +2221,27 @@
         <v xml:space="preserve">    Kambiyo İşlemleri Karı (Zararı)</v>
       </c>
       <c r="B29">
-        <v>449794000</v>
+        <v>764000000</v>
       </c>
       <c r="C29">
+        <v>450000000</v>
+      </c>
+      <c r="D29">
         <v>-1717664000</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>-187890000</v>
       </c>
-      <c r="E29">
-        <v>48397000</v>
-      </c>
       <c r="F29">
+        <v>91000000</v>
+      </c>
+      <c r="G29">
+        <v>48000000</v>
+      </c>
+      <c r="H29">
         <v>1395480000</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>1131705000</v>
       </c>
     </row>
@@ -1941,21 +2250,27 @@
         <v xml:space="preserve">    DİĞER FAALİYET GELİRLERİ</v>
       </c>
       <c r="B30">
-        <v>49323000</v>
+        <v>1168000000</v>
       </c>
       <c r="C30">
+        <v>49000000</v>
+      </c>
+      <c r="D30">
         <v>2689587000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>2629700000</v>
       </c>
-      <c r="E30">
-        <v>924000</v>
-      </c>
       <c r="F30">
+        <v>1000000</v>
+      </c>
+      <c r="G30">
+        <v>1000000</v>
+      </c>
+      <c r="H30">
         <v>2065000</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>60000</v>
       </c>
     </row>
@@ -1964,21 +2279,27 @@
         <v xml:space="preserve">    FAALİYET BRÜT KÂRI</v>
       </c>
       <c r="B31">
-        <v>7238639000</v>
+        <v>16170000000</v>
       </c>
       <c r="C31">
+        <v>7237000000</v>
+      </c>
+      <c r="D31">
         <v>14443326000</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>7439808000</v>
       </c>
-      <c r="E31">
-        <v>837242000</v>
-      </c>
       <c r="F31">
+        <v>1820000000</v>
+      </c>
+      <c r="G31">
+        <v>838000000</v>
+      </c>
+      <c r="H31">
         <v>1689497000</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>1328722000</v>
       </c>
     </row>
@@ -1987,21 +2308,27 @@
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
       <c r="B32">
-        <v>-1679421000</v>
+        <v>-4774000000</v>
       </c>
       <c r="C32">
+        <v>-1679000000</v>
+      </c>
+      <c r="D32">
         <v>-2756632000</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>-865212000</v>
       </c>
-      <c r="E32">
-        <v>-157000</v>
-      </c>
       <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>-1070000</v>
       </c>
-      <c r="G32">
+      <c r="I32">
         <v>0</v>
       </c>
     </row>
@@ -2010,21 +2337,27 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B33">
-        <v>-1938968000</v>
+        <v>-4115000000</v>
       </c>
       <c r="C33">
+        <v>-1939000000</v>
+      </c>
+      <c r="D33">
         <v>-3752865000</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>-1759264000</v>
       </c>
-      <c r="E33">
-        <v>-317639000</v>
-      </c>
       <c r="F33">
+        <v>-706000000</v>
+      </c>
+      <c r="G33">
+        <v>-318000000</v>
+      </c>
+      <c r="H33">
         <v>-775550000</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-562172000</v>
       </c>
     </row>
@@ -2033,21 +2366,27 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B34">
-        <v>2709637000</v>
+        <v>5414000000</v>
       </c>
       <c r="C34">
+        <v>2709000000</v>
+      </c>
+      <c r="D34">
         <v>6863316000</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>4426718000</v>
       </c>
-      <c r="E34">
-        <v>475616000</v>
-      </c>
       <c r="F34">
+        <v>1014000000</v>
+      </c>
+      <c r="G34">
+        <v>476000000</v>
+      </c>
+      <c r="H34">
         <v>847042000</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>725514000</v>
       </c>
     </row>
@@ -2073,6 +2412,12 @@
       <c r="G35">
         <v>0</v>
       </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2096,6 +2441,12 @@
       <c r="G36">
         <v>0</v>
       </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2119,27 +2470,39 @@
       <c r="G37">
         <v>0</v>
       </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B38">
-        <v>2709637000</v>
+        <v>5414000000</v>
       </c>
       <c r="C38">
+        <v>2709000000</v>
+      </c>
+      <c r="D38">
         <v>6863316000</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>4426718000</v>
       </c>
-      <c r="E38">
-        <v>475616000</v>
-      </c>
       <c r="F38">
+        <v>1014000000</v>
+      </c>
+      <c r="G38">
+        <v>476000000</v>
+      </c>
+      <c r="H38">
         <v>847042000</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>725514000</v>
       </c>
     </row>
@@ -2148,21 +2511,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B39">
-        <v>-788537000</v>
+        <v>-1546000000</v>
       </c>
       <c r="C39">
+        <v>-788000000</v>
+      </c>
+      <c r="D39">
         <v>-1207379000</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-498469000</v>
       </c>
-      <c r="E39">
-        <v>-105842000</v>
-      </c>
       <c r="F39">
+        <v>-249000000</v>
+      </c>
+      <c r="G39">
+        <v>-106000000</v>
+      </c>
+      <c r="H39">
         <v>-178587000</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>-164932000</v>
       </c>
     </row>
@@ -2171,21 +2540,27 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B40">
-        <v>-2045098000</v>
+        <v>-3362000000</v>
       </c>
       <c r="C40">
+        <v>-2045000000</v>
+      </c>
+      <c r="D40">
         <v>-368957000</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>-6250000</v>
       </c>
-      <c r="E40">
-        <v>-136510000</v>
-      </c>
       <c r="F40">
+        <v>-293000000</v>
+      </c>
+      <c r="G40">
+        <v>-137000000</v>
+      </c>
+      <c r="H40">
         <v>-75171000</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>-77746000</v>
       </c>
     </row>
@@ -2197,18 +2572,24 @@
         <v>0</v>
       </c>
       <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
         <v>-838422000</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>-492219000</v>
       </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
       <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>-103416000</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>-87186000</v>
       </c>
     </row>
@@ -2217,21 +2598,27 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Gelir Etkisi</v>
       </c>
       <c r="B42">
-        <v>1256561000</v>
+        <v>1816000000</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1257000000</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>30668000</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>44000000</v>
       </c>
       <c r="G42">
+        <v>31000000</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>0</v>
       </c>
     </row>
@@ -2240,21 +2627,27 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B43">
-        <v>1921100000</v>
+        <v>3868000000</v>
       </c>
       <c r="C43">
+        <v>1921000000</v>
+      </c>
+      <c r="D43">
         <v>5655937000</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>3928249000</v>
       </c>
-      <c r="E43">
-        <v>369774000</v>
-      </c>
       <c r="F43">
+        <v>765000000</v>
+      </c>
+      <c r="G43">
+        <v>370000000</v>
+      </c>
+      <c r="H43">
         <v>668455000</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>560582000</v>
       </c>
     </row>
@@ -2263,21 +2656,27 @@
         <v xml:space="preserve">    DÖNEM NET KARI VEYA ZARARI</v>
       </c>
       <c r="B44">
-        <v>1921100000</v>
+        <v>3868000000</v>
       </c>
       <c r="C44">
+        <v>1921000000</v>
+      </c>
+      <c r="D44">
         <v>5655937000</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>3928249000</v>
       </c>
-      <c r="E44">
-        <v>369774000</v>
-      </c>
       <c r="F44">
+        <v>765000000</v>
+      </c>
+      <c r="G44">
+        <v>370000000</v>
+      </c>
+      <c r="H44">
         <v>668455000</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>560582000</v>
       </c>
     </row>
@@ -2286,21 +2685,27 @@
         <v xml:space="preserve">    Grubun Karı (Zararı)</v>
       </c>
       <c r="B45">
-        <v>1921100000</v>
+        <v>3868000000</v>
       </c>
       <c r="C45">
+        <v>1921000000</v>
+      </c>
+      <c r="D45">
         <v>5655937000</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>3928249000</v>
       </c>
-      <c r="E45">
-        <v>369774000</v>
-      </c>
       <c r="F45">
+        <v>765000000</v>
+      </c>
+      <c r="G45">
+        <v>370000000</v>
+      </c>
+      <c r="H45">
         <v>668455000</v>
       </c>
-      <c r="G45">
+      <c r="I45">
         <v>560582000</v>
       </c>
     </row>
@@ -2326,17 +2731,23 @@
       <c r="G46">
         <v>0</v>
       </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:I46"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2345,6 +2756,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2352,21 +2765,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
     </row>
@@ -2380,15 +2799,24 @@
         <v xml:space="preserve">    FAİZ GELİRLERİ</v>
       </c>
       <c r="B3">
-        <v>17036957000</v>
+        <v>19433000000</v>
       </c>
       <c r="C3">
+        <v>17036000000</v>
+      </c>
+      <c r="D3">
         <v>17502490000</v>
       </c>
       <c r="E3">
-        <v>794703000</v>
+        <v>7211834000</v>
       </c>
       <c r="F3">
+        <v>951000000</v>
+      </c>
+      <c r="G3">
+        <v>795000000</v>
+      </c>
+      <c r="H3">
         <v>95953000</v>
       </c>
     </row>
@@ -2402,15 +2830,24 @@
         <v xml:space="preserve">    Kredilerden Alınan Faizler</v>
       </c>
       <c r="B5">
-        <v>12545292000</v>
+        <v>13771000000</v>
       </c>
       <c r="C5">
+        <v>12545000000</v>
+      </c>
+      <c r="D5">
         <v>12301557000</v>
       </c>
       <c r="E5">
-        <v>1000</v>
+        <v>4447673000</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -2419,15 +2856,24 @@
         <v xml:space="preserve">    Zorunlu Karşılıklardan Alınan Faizler</v>
       </c>
       <c r="B6">
-        <v>2275479000</v>
+        <v>2613000000</v>
       </c>
       <c r="C6">
+        <v>2276000000</v>
+      </c>
+      <c r="D6">
         <v>2139521000</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>882627000</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
     </row>
@@ -2436,15 +2882,24 @@
         <v xml:space="preserve">    Bankalardan Alınan Faizler</v>
       </c>
       <c r="B7">
-        <v>201341000</v>
+        <v>253000000</v>
       </c>
       <c r="C7">
+        <v>201000000</v>
+      </c>
+      <c r="D7">
         <v>786800000</v>
       </c>
       <c r="E7">
-        <v>310716000</v>
+        <v>1027344000</v>
       </c>
       <c r="F7">
+        <v>14000000</v>
+      </c>
+      <c r="G7">
+        <v>311000000</v>
+      </c>
+      <c r="H7">
         <v>95953000</v>
       </c>
     </row>
@@ -2453,15 +2908,24 @@
         <v xml:space="preserve">    Para Piyasası İşlemlerinden Alınan Faizler</v>
       </c>
       <c r="B8">
-        <v>164000</v>
+        <v>8000000</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>417841000</v>
       </c>
       <c r="E8">
-        <v>482897000</v>
+        <v>263159000</v>
       </c>
       <c r="F8">
+        <v>925000000</v>
+      </c>
+      <c r="G8">
+        <v>483000000</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
@@ -2470,15 +2934,24 @@
         <v xml:space="preserve">    Menkul Değerlerden Alınan Faizler</v>
       </c>
       <c r="B9">
-        <v>2011240000</v>
+        <v>2788000000</v>
       </c>
       <c r="C9">
+        <v>2011000000</v>
+      </c>
+      <c r="D9">
         <v>1856755000</v>
       </c>
       <c r="E9">
-        <v>1089000</v>
+        <v>591031000</v>
       </c>
       <c r="F9">
+        <v>12000000</v>
+      </c>
+      <c r="G9">
+        <v>1000000</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -2492,10 +2965,19 @@
       <c r="C10">
         <v>0</v>
       </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>0</v>
       </c>
     </row>
@@ -2504,15 +2986,24 @@
         <v xml:space="preserve">    Diğer Faiz Gelirleri</v>
       </c>
       <c r="B11">
-        <v>3441000</v>
+        <v>0</v>
       </c>
       <c r="C11">
+        <v>3000000</v>
+      </c>
+      <c r="D11">
         <v>16000</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
@@ -2521,15 +3012,24 @@
         <v xml:space="preserve">    FAİZ GİDERLERİ (-)</v>
       </c>
       <c r="B12">
-        <v>-11726606000</v>
+        <v>-13942000000</v>
       </c>
       <c r="C12">
+        <v>-11727000000</v>
+      </c>
+      <c r="D12">
         <v>-12057470000</v>
       </c>
       <c r="E12">
-        <v>-6136000</v>
+        <v>-4611216000</v>
       </c>
       <c r="F12">
+        <v>-10000000</v>
+      </c>
+      <c r="G12">
+        <v>-6000000</v>
+      </c>
+      <c r="H12">
         <v>-234000</v>
       </c>
     </row>
@@ -2543,15 +3043,24 @@
         <v xml:space="preserve">    Mevduata Verilen Faizler</v>
       </c>
       <c r="B14">
-        <v>-11395885000</v>
+        <v>-13396000000</v>
       </c>
       <c r="C14">
+        <v>-11396000000</v>
+      </c>
+      <c r="D14">
         <v>-11916059000</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>-4607337000</v>
       </c>
       <c r="F14">
+        <v>-1000000</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>0</v>
       </c>
     </row>
@@ -2560,15 +3069,24 @@
         <v xml:space="preserve">    Kullanılan Kredilere Verilen Faizler</v>
       </c>
       <c r="B15">
-        <v>-973000</v>
+        <v>0</v>
       </c>
       <c r="C15">
+        <v>-1000000</v>
+      </c>
+      <c r="D15">
         <v>562000</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>-562000</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>3000</v>
       </c>
     </row>
@@ -2577,15 +3095,24 @@
         <v xml:space="preserve">    Para Piyasası İşlemlerine Verilen Faizler</v>
       </c>
       <c r="B16">
-        <v>-292721000</v>
+        <v>-499000000</v>
       </c>
       <c r="C16">
+        <v>-293000000</v>
+      </c>
+      <c r="D16">
         <v>-110078000</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>0</v>
       </c>
     </row>
@@ -2599,10 +3126,19 @@
       <c r="C17">
         <v>0</v>
       </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>0</v>
       </c>
     </row>
@@ -2611,15 +3147,24 @@
         <v xml:space="preserve">    Diğer Faiz Giderleri</v>
       </c>
       <c r="B18">
-        <v>-7348000</v>
+        <v>-23000000</v>
       </c>
       <c r="C18">
+        <v>-7000000</v>
+      </c>
+      <c r="D18">
         <v>-12011000</v>
       </c>
       <c r="E18">
-        <v>-4125000</v>
+        <v>-1859000</v>
       </c>
       <c r="F18">
+        <v>-7000000</v>
+      </c>
+      <c r="G18">
+        <v>-4000000</v>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
     </row>
@@ -2628,15 +3173,24 @@
         <v xml:space="preserve">    NET FAİZ GELİRİ VEYA GİDERİ</v>
       </c>
       <c r="B19">
-        <v>5310351000</v>
+        <v>5491000000</v>
       </c>
       <c r="C19">
+        <v>5309000000</v>
+      </c>
+      <c r="D19">
         <v>5445020000</v>
       </c>
       <c r="E19">
-        <v>788567000</v>
+        <v>2600618000</v>
       </c>
       <c r="F19">
+        <v>941000000</v>
+      </c>
+      <c r="G19">
+        <v>789000000</v>
+      </c>
+      <c r="H19">
         <v>95719000</v>
       </c>
     </row>
@@ -2650,15 +3204,24 @@
         <v xml:space="preserve">    NET ÜCRET VE KOMİSYON GELİRLERİ VEYA GİDERLERİ</v>
       </c>
       <c r="B21">
-        <v>2490378000</v>
+        <v>2976000000</v>
       </c>
       <c r="C21">
+        <v>2490000000</v>
+      </c>
+      <c r="D21">
         <v>2552370000</v>
       </c>
       <c r="E21">
-        <v>-646000</v>
+        <v>1117568000</v>
       </c>
       <c r="F21">
+        <v>-2000000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>-724000</v>
       </c>
     </row>
@@ -2667,15 +3230,24 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B22">
-        <v>3909076000</v>
+        <v>4521000000</v>
       </c>
       <c r="C22">
+        <v>3909000000</v>
+      </c>
+      <c r="D22">
         <v>4103925000</v>
       </c>
       <c r="E22">
-        <v>1000</v>
+        <v>1459666000</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>0</v>
       </c>
     </row>
@@ -2684,15 +3256,24 @@
         <v xml:space="preserve">    Verilen Ücret ve Komisyonlar (-)</v>
       </c>
       <c r="B23">
-        <v>-1418698000</v>
+        <v>-1545000000</v>
       </c>
       <c r="C23">
+        <v>-1419000000</v>
+      </c>
+      <c r="D23">
         <v>-1551555000</v>
       </c>
       <c r="E23">
-        <v>-647000</v>
+        <v>-342098000</v>
       </c>
       <c r="F23">
+        <v>-2000000</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>-724000</v>
       </c>
     </row>
@@ -2701,15 +3282,24 @@
         <v xml:space="preserve">    PERSONEL GİDERLERİ (-)</v>
       </c>
       <c r="B24">
-        <v>-910352000</v>
+        <v>-956000000</v>
       </c>
       <c r="C24">
+        <v>-910000000</v>
+      </c>
+      <c r="D24">
         <v>-683856000</v>
       </c>
       <c r="E24">
-        <v>-43826000</v>
+        <v>-286316000</v>
       </c>
       <c r="F24">
+        <v>-56000000</v>
+      </c>
+      <c r="G24">
+        <v>-44000000</v>
+      </c>
+      <c r="H24">
         <v>-24799000</v>
       </c>
     </row>
@@ -2723,10 +3313,19 @@
       <c r="C25">
         <v>0</v>
       </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
@@ -2735,15 +3334,24 @@
         <v xml:space="preserve">    TİCARİ KAR VEYA ZARAR (Net)</v>
       </c>
       <c r="B26">
-        <v>-611413000</v>
+        <v>-653000000</v>
       </c>
       <c r="C26">
+        <v>-611000000</v>
+      </c>
+      <c r="D26">
         <v>-1053759000</v>
       </c>
       <c r="E26">
-        <v>48397000</v>
+        <v>-727078000</v>
       </c>
       <c r="F26">
+        <v>43000000</v>
+      </c>
+      <c r="G26">
+        <v>48000000</v>
+      </c>
+      <c r="H26">
         <v>263775000</v>
       </c>
     </row>
@@ -2752,15 +3360,24 @@
         <v xml:space="preserve">    Sermaye Piyasası İşlemleri Karı (Zararı)</v>
       </c>
       <c r="B27">
-        <v>-13419000</v>
+        <v>0</v>
       </c>
       <c r="C27">
+        <v>-13000000</v>
+      </c>
+      <c r="D27">
         <v>-57749000</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>675000</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>0</v>
       </c>
     </row>
@@ -2769,15 +3386,24 @@
         <v xml:space="preserve">    Türev Finansal İşlemlerden Kar (Zarar)</v>
       </c>
       <c r="B28">
-        <v>-1047788000</v>
+        <v>-967000000</v>
       </c>
       <c r="C28">
+        <v>-1048000000</v>
+      </c>
+      <c r="D28">
         <v>533764000</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>-448863000</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>0</v>
       </c>
     </row>
@@ -2786,15 +3412,24 @@
         <v xml:space="preserve">    Kambiyo İşlemleri Karı (Zararı)</v>
       </c>
       <c r="B29">
-        <v>449794000</v>
+        <v>314000000</v>
       </c>
       <c r="C29">
+        <v>450000000</v>
+      </c>
+      <c r="D29">
         <v>-1529774000</v>
       </c>
       <c r="E29">
-        <v>48397000</v>
+        <v>-278890000</v>
       </c>
       <c r="F29">
+        <v>43000000</v>
+      </c>
+      <c r="G29">
+        <v>48000000</v>
+      </c>
+      <c r="H29">
         <v>263775000</v>
       </c>
     </row>
@@ -2803,15 +3438,24 @@
         <v xml:space="preserve">    DİĞER FAALİYET GELİRLERİ</v>
       </c>
       <c r="B30">
-        <v>49323000</v>
+        <v>1119000000</v>
       </c>
       <c r="C30">
+        <v>49000000</v>
+      </c>
+      <c r="D30">
         <v>59887000</v>
       </c>
       <c r="E30">
-        <v>924000</v>
+        <v>2628700000</v>
       </c>
       <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1000000</v>
+      </c>
+      <c r="H30">
         <v>2005000</v>
       </c>
     </row>
@@ -2820,15 +3464,24 @@
         <v xml:space="preserve">    FAALİYET BRÜT KÂRI</v>
       </c>
       <c r="B31">
-        <v>7238639000</v>
+        <v>8933000000</v>
       </c>
       <c r="C31">
+        <v>7237000000</v>
+      </c>
+      <c r="D31">
         <v>7003518000</v>
       </c>
       <c r="E31">
-        <v>837242000</v>
+        <v>5619808000</v>
       </c>
       <c r="F31">
+        <v>982000000</v>
+      </c>
+      <c r="G31">
+        <v>838000000</v>
+      </c>
+      <c r="H31">
         <v>360775000</v>
       </c>
     </row>
@@ -2837,15 +3490,24 @@
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
       <c r="B32">
-        <v>-1679421000</v>
+        <v>-3095000000</v>
       </c>
       <c r="C32">
+        <v>-1679000000</v>
+      </c>
+      <c r="D32">
         <v>-1891420000</v>
       </c>
       <c r="E32">
-        <v>-157000</v>
+        <v>-865212000</v>
       </c>
       <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>-1070000</v>
       </c>
     </row>
@@ -2854,15 +3516,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B33">
-        <v>-1938968000</v>
+        <v>-2176000000</v>
       </c>
       <c r="C33">
+        <v>-1939000000</v>
+      </c>
+      <c r="D33">
         <v>-1993601000</v>
       </c>
       <c r="E33">
-        <v>-317639000</v>
+        <v>-1053264000</v>
       </c>
       <c r="F33">
+        <v>-388000000</v>
+      </c>
+      <c r="G33">
+        <v>-318000000</v>
+      </c>
+      <c r="H33">
         <v>-213378000</v>
       </c>
     </row>
@@ -2871,15 +3542,24 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B34">
-        <v>2709637000</v>
+        <v>2705000000</v>
       </c>
       <c r="C34">
+        <v>2709000000</v>
+      </c>
+      <c r="D34">
         <v>2436598000</v>
       </c>
       <c r="E34">
-        <v>475616000</v>
+        <v>3412718000</v>
       </c>
       <c r="F34">
+        <v>538000000</v>
+      </c>
+      <c r="G34">
+        <v>476000000</v>
+      </c>
+      <c r="H34">
         <v>121528000</v>
       </c>
     </row>
@@ -2893,10 +3573,19 @@
       <c r="C35">
         <v>0</v>
       </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>0</v>
       </c>
     </row>
@@ -2910,10 +3599,19 @@
       <c r="C36">
         <v>0</v>
       </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>0</v>
       </c>
     </row>
@@ -2927,10 +3625,19 @@
       <c r="C37">
         <v>0</v>
       </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>0</v>
       </c>
     </row>
@@ -2939,15 +3646,24 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B38">
-        <v>2709637000</v>
+        <v>2705000000</v>
       </c>
       <c r="C38">
+        <v>2709000000</v>
+      </c>
+      <c r="D38">
         <v>2436598000</v>
       </c>
       <c r="E38">
-        <v>475616000</v>
+        <v>3412718000</v>
       </c>
       <c r="F38">
+        <v>538000000</v>
+      </c>
+      <c r="G38">
+        <v>476000000</v>
+      </c>
+      <c r="H38">
         <v>121528000</v>
       </c>
     </row>
@@ -2956,15 +3672,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B39">
-        <v>-788537000</v>
+        <v>-758000000</v>
       </c>
       <c r="C39">
+        <v>-788000000</v>
+      </c>
+      <c r="D39">
         <v>-708910000</v>
       </c>
       <c r="E39">
-        <v>-105842000</v>
+        <v>-249469000</v>
       </c>
       <c r="F39">
+        <v>-143000000</v>
+      </c>
+      <c r="G39">
+        <v>-106000000</v>
+      </c>
+      <c r="H39">
         <v>-13655000</v>
       </c>
     </row>
@@ -2973,15 +3698,24 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B40">
-        <v>-2045098000</v>
+        <v>-1317000000</v>
       </c>
       <c r="C40">
+        <v>-2045000000</v>
+      </c>
+      <c r="D40">
         <v>-362707000</v>
       </c>
       <c r="E40">
-        <v>-136510000</v>
+        <v>286750000</v>
       </c>
       <c r="F40">
+        <v>-156000000</v>
+      </c>
+      <c r="G40">
+        <v>-137000000</v>
+      </c>
+      <c r="H40">
         <v>2575000</v>
       </c>
     </row>
@@ -2993,12 +3727,21 @@
         <v>0</v>
       </c>
       <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
         <v>-346203000</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>-492219000</v>
       </c>
       <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>-16230000</v>
       </c>
     </row>
@@ -3007,15 +3750,24 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Gelir Etkisi</v>
       </c>
       <c r="B42">
-        <v>1256561000</v>
+        <v>559000000</v>
       </c>
       <c r="C42">
+        <v>1257000000</v>
+      </c>
+      <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>30668000</v>
+        <v>-44000000</v>
       </c>
       <c r="F42">
+        <v>13000000</v>
+      </c>
+      <c r="G42">
+        <v>31000000</v>
+      </c>
+      <c r="H42">
         <v>0</v>
       </c>
     </row>
@@ -3024,15 +3776,24 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B43">
-        <v>1921100000</v>
+        <v>1947000000</v>
       </c>
       <c r="C43">
+        <v>1921000000</v>
+      </c>
+      <c r="D43">
         <v>1727688000</v>
       </c>
       <c r="E43">
-        <v>369774000</v>
+        <v>3163249000</v>
       </c>
       <c r="F43">
+        <v>395000000</v>
+      </c>
+      <c r="G43">
+        <v>370000000</v>
+      </c>
+      <c r="H43">
         <v>107873000</v>
       </c>
     </row>
@@ -3041,15 +3802,24 @@
         <v xml:space="preserve">    DÖNEM NET KARI VEYA ZARARI</v>
       </c>
       <c r="B44">
-        <v>1921100000</v>
+        <v>1947000000</v>
       </c>
       <c r="C44">
+        <v>1921000000</v>
+      </c>
+      <c r="D44">
         <v>1727688000</v>
       </c>
       <c r="E44">
-        <v>369774000</v>
+        <v>3163249000</v>
       </c>
       <c r="F44">
+        <v>395000000</v>
+      </c>
+      <c r="G44">
+        <v>370000000</v>
+      </c>
+      <c r="H44">
         <v>107873000</v>
       </c>
     </row>
@@ -3058,15 +3828,24 @@
         <v xml:space="preserve">    Grubun Karı (Zararı)</v>
       </c>
       <c r="B45">
-        <v>1921100000</v>
+        <v>1947000000</v>
       </c>
       <c r="C45">
+        <v>1921000000</v>
+      </c>
+      <c r="D45">
         <v>1727688000</v>
       </c>
       <c r="E45">
-        <v>369774000</v>
+        <v>3163249000</v>
       </c>
       <c r="F45">
+        <v>395000000</v>
+      </c>
+      <c r="G45">
+        <v>370000000</v>
+      </c>
+      <c r="H45">
         <v>107873000</v>
       </c>
     </row>
@@ -3080,23 +3859,32 @@
       <c r="C46">
         <v>0</v>
       </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:I46"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3105,6 +3893,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3112,21 +3902,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
     </row>
@@ -3140,15 +3936,18 @@
         <v xml:space="preserve">    FAİZ GELİRLERİ</v>
       </c>
       <c r="B3">
-        <v>42702578000</v>
+        <v>61183324000</v>
       </c>
       <c r="C3">
+        <v>42701324000</v>
+      </c>
+      <c r="D3">
         <v>26460324000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>9053787000</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>296810000</v>
       </c>
     </row>
@@ -3162,15 +3961,18 @@
         <v xml:space="preserve">    Kredilerden Alınan Faizler</v>
       </c>
       <c r="B5">
-        <v>29294521000</v>
+        <v>43065230000</v>
       </c>
       <c r="C5">
+        <v>29294230000</v>
+      </c>
+      <c r="D5">
         <v>16749230000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>4447673000</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -3179,15 +3981,18 @@
         <v xml:space="preserve">    Zorunlu Karşılıklardan Alınan Faizler</v>
       </c>
       <c r="B6">
-        <v>5297627000</v>
+        <v>7911148000</v>
       </c>
       <c r="C6">
+        <v>5298148000</v>
+      </c>
+      <c r="D6">
         <v>3022148000</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>882627000</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>0</v>
       </c>
     </row>
@@ -3196,15 +4001,18 @@
         <v xml:space="preserve">    Bankalardan Alınan Faizler</v>
       </c>
       <c r="B7">
-        <v>2029769000</v>
+        <v>2268144000</v>
       </c>
       <c r="C7">
+        <v>2029144000</v>
+      </c>
+      <c r="D7">
         <v>2139144000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1448297000</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>181219000</v>
       </c>
     </row>
@@ -3213,15 +4021,18 @@
         <v xml:space="preserve">    Para Piyasası İşlemlerinden Alınan Faizler</v>
       </c>
       <c r="B8">
-        <v>1606267000</v>
+        <v>689000000</v>
       </c>
       <c r="C8">
+        <v>1606000000</v>
+      </c>
+      <c r="D8">
         <v>2089000000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1671159000</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>115591000</v>
       </c>
     </row>
@@ -3230,15 +4041,18 @@
         <v xml:space="preserve">    Menkul Değerlerden Alınan Faizler</v>
       </c>
       <c r="B9">
-        <v>4470937000</v>
+        <v>7246786000</v>
       </c>
       <c r="C9">
+        <v>4470786000</v>
+      </c>
+      <c r="D9">
         <v>2460786000</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>604031000</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -3255,7 +4069,10 @@
       <c r="D10">
         <v>0</v>
       </c>
-      <c r="F10">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>0</v>
       </c>
     </row>
@@ -3264,15 +4081,18 @@
         <v xml:space="preserve">    Diğer Faiz Gelirleri</v>
       </c>
       <c r="B11">
-        <v>3457000</v>
+        <v>3016000</v>
       </c>
       <c r="C11">
+        <v>3016000</v>
+      </c>
+      <c r="D11">
         <v>16000</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="F11">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
@@ -3281,15 +4101,18 @@
         <v xml:space="preserve">    FAİZ GİDERLERİ (-)</v>
       </c>
       <c r="B12">
-        <v>-28405156000</v>
+        <v>-42337686000</v>
       </c>
       <c r="C12">
+        <v>-28405686000</v>
+      </c>
+      <c r="D12">
         <v>-16684686000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-4627450000</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-4134000</v>
       </c>
     </row>
@@ -3303,15 +4126,18 @@
         <v xml:space="preserve">    Mevduata Verilen Faizler</v>
       </c>
       <c r="B14">
-        <v>-27920281000</v>
+        <v>-41315396000</v>
       </c>
       <c r="C14">
+        <v>-27920396000</v>
+      </c>
+      <c r="D14">
         <v>-16524396000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>-4608337000</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>0</v>
       </c>
     </row>
@@ -3320,15 +4146,18 @@
         <v xml:space="preserve">    Kullanılan Kredilere Verilen Faizler</v>
       </c>
       <c r="B15">
-        <v>-973000</v>
+        <v>-1000000</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>-1000000</v>
       </c>
       <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>-559000</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>0</v>
       </c>
     </row>
@@ -3337,15 +4166,18 @@
         <v xml:space="preserve">    Para Piyasası İşlemlerine Verilen Faizler</v>
       </c>
       <c r="B16">
-        <v>-402803000</v>
+        <v>-902082000</v>
       </c>
       <c r="C16">
+        <v>-403082000</v>
+      </c>
+      <c r="D16">
         <v>-110082000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-4000</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>0</v>
       </c>
     </row>
@@ -3362,7 +4194,10 @@
       <c r="D17">
         <v>0</v>
       </c>
-      <c r="F17">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>0</v>
       </c>
     </row>
@@ -3371,15 +4206,18 @@
         <v xml:space="preserve">    Diğer Faiz Giderleri</v>
       </c>
       <c r="B18">
-        <v>-28093000</v>
+        <v>-43870000</v>
       </c>
       <c r="C18">
+        <v>-27870000</v>
+      </c>
+      <c r="D18">
         <v>-24870000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>-12859000</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>-3525000</v>
       </c>
     </row>
@@ -3388,15 +4226,18 @@
         <v xml:space="preserve">    NET FAİZ GELİRİ VEYA GİDERİ</v>
       </c>
       <c r="B19">
-        <v>14297422000</v>
+        <v>18845638000</v>
       </c>
       <c r="C19">
+        <v>14295638000</v>
+      </c>
+      <c r="D19">
         <v>9775638000</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>4426337000</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>292676000</v>
       </c>
     </row>
@@ -3410,15 +4251,18 @@
         <v xml:space="preserve">    NET ÜCRET VE KOMİSYON GELİRLERİ VEYA GİDERLERİ</v>
       </c>
       <c r="B21">
-        <v>6158962000</v>
+        <v>9135938000</v>
       </c>
       <c r="C21">
+        <v>6157938000</v>
+      </c>
+      <c r="D21">
         <v>3667938000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1114844000</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>-724000</v>
       </c>
     </row>
@@ -3427,15 +4271,18 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B22">
-        <v>9472666000</v>
+        <v>13993591000</v>
       </c>
       <c r="C22">
+        <v>9472591000</v>
+      </c>
+      <c r="D22">
         <v>5563591000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>1459666000</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>0</v>
       </c>
     </row>
@@ -3444,15 +4291,18 @@
         <v xml:space="preserve">    Verilen Ücret ve Komisyonlar (-)</v>
       </c>
       <c r="B23">
-        <v>-3313704000</v>
+        <v>-4857653000</v>
       </c>
       <c r="C23">
+        <v>-3314653000</v>
+      </c>
+      <c r="D23">
         <v>-1895653000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-344822000</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>-724000</v>
       </c>
     </row>
@@ -3461,15 +4311,18 @@
         <v xml:space="preserve">    PERSONEL GİDERLERİ (-)</v>
       </c>
       <c r="B24">
-        <v>-1936698000</v>
+        <v>-2836172000</v>
       </c>
       <c r="C24">
+        <v>-1936172000</v>
+      </c>
+      <c r="D24">
         <v>-1070172000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>-411115000</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>-65830000</v>
       </c>
     </row>
@@ -3486,7 +4339,10 @@
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="F25">
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
@@ -3495,15 +4351,18 @@
         <v xml:space="preserve">    TİCARİ KAR VEYA ZARAR (Net)</v>
       </c>
       <c r="B26">
-        <v>-2349647000</v>
+        <v>-3044837000</v>
       </c>
       <c r="C26">
+        <v>-2348837000</v>
+      </c>
+      <c r="D26">
         <v>-1689837000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>-372303000</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1395480000</v>
       </c>
     </row>
@@ -3512,15 +4371,18 @@
         <v xml:space="preserve">    Sermaye Piyasası İşlemleri Karı (Zararı)</v>
       </c>
       <c r="B27">
-        <v>-70493000</v>
+        <v>-70074000</v>
       </c>
       <c r="C27">
+        <v>-70074000</v>
+      </c>
+      <c r="D27">
         <v>-57074000</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>675000</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>0</v>
       </c>
     </row>
@@ -3529,15 +4391,18 @@
         <v xml:space="preserve">    Türev Finansal İşlemlerden Kar (Zarar)</v>
       </c>
       <c r="B28">
-        <v>-962887000</v>
+        <v>-1930099000</v>
       </c>
       <c r="C28">
+        <v>-963099000</v>
+      </c>
+      <c r="D28">
         <v>84901000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-448863000</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>0</v>
       </c>
     </row>
@@ -3546,15 +4411,18 @@
         <v xml:space="preserve">    Kambiyo İşlemleri Karı (Zararı)</v>
       </c>
       <c r="B29">
-        <v>-1316267000</v>
+        <v>-1044664000</v>
       </c>
       <c r="C29">
+        <v>-1315664000</v>
+      </c>
+      <c r="D29">
         <v>-1717664000</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>75885000</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>1395480000</v>
       </c>
     </row>
@@ -3563,15 +4431,18 @@
         <v xml:space="preserve">    DİĞER FAALİYET GELİRLERİ</v>
       </c>
       <c r="B30">
-        <v>2737986000</v>
+        <v>3856587000</v>
       </c>
       <c r="C30">
+        <v>2737587000</v>
+      </c>
+      <c r="D30">
         <v>2689587000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>2631705000</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>2065000</v>
       </c>
     </row>
@@ -3580,15 +4451,18 @@
         <v xml:space="preserve">    FAALİYET BRÜT KÂRI</v>
       </c>
       <c r="B31">
-        <v>20844723000</v>
+        <v>28793326000</v>
       </c>
       <c r="C31">
+        <v>20842326000</v>
+      </c>
+      <c r="D31">
         <v>14443326000</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>7800583000</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>1689497000</v>
       </c>
     </row>
@@ -3597,15 +4471,18 @@
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
       <c r="B32">
-        <v>-4435896000</v>
+        <v>-7530632000</v>
       </c>
       <c r="C32">
+        <v>-4435632000</v>
+      </c>
+      <c r="D32">
         <v>-2756632000</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>-866282000</v>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>-1070000</v>
       </c>
     </row>
@@ -3614,15 +4491,18 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B33">
-        <v>-5374194000</v>
+        <v>-7161865000</v>
       </c>
       <c r="C33">
+        <v>-5373865000</v>
+      </c>
+      <c r="D33">
         <v>-3752865000</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>-1972642000</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>-775550000</v>
       </c>
     </row>
@@ -3631,15 +4511,18 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B34">
-        <v>9097337000</v>
+        <v>11263316000</v>
       </c>
       <c r="C34">
+        <v>9096316000</v>
+      </c>
+      <c r="D34">
         <v>6863316000</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>4548246000</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>847042000</v>
       </c>
     </row>
@@ -3656,7 +4539,10 @@
       <c r="D35">
         <v>0</v>
       </c>
-      <c r="F35">
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>0</v>
       </c>
     </row>
@@ -3673,7 +4559,10 @@
       <c r="D36">
         <v>0</v>
       </c>
-      <c r="F36">
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>0</v>
       </c>
     </row>
@@ -3690,7 +4579,10 @@
       <c r="D37">
         <v>0</v>
       </c>
-      <c r="F37">
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>0</v>
       </c>
     </row>
@@ -3699,15 +4591,18 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B38">
-        <v>9097337000</v>
+        <v>11263316000</v>
       </c>
       <c r="C38">
+        <v>9096316000</v>
+      </c>
+      <c r="D38">
         <v>6863316000</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>4548246000</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>847042000</v>
       </c>
     </row>
@@ -3716,15 +4611,18 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B39">
-        <v>-1890074000</v>
+        <v>-2504379000</v>
       </c>
       <c r="C39">
+        <v>-1889379000</v>
+      </c>
+      <c r="D39">
         <v>-1207379000</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-512124000</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>-178587000</v>
       </c>
     </row>
@@ -3733,15 +4631,18 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B40">
-        <v>-2277545000</v>
+        <v>-3437957000</v>
       </c>
       <c r="C40">
+        <v>-2276957000</v>
+      </c>
+      <c r="D40">
         <v>-368957000</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>-3675000</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>-75171000</v>
       </c>
     </row>
@@ -3756,9 +4657,12 @@
         <v>-838422000</v>
       </c>
       <c r="D41">
+        <v>-838422000</v>
+      </c>
+      <c r="E41">
         <v>-508449000</v>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>-103416000</v>
       </c>
     </row>
@@ -3767,15 +4671,18 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Gelir Etkisi</v>
       </c>
       <c r="B42">
-        <v>1225893000</v>
+        <v>1772000000</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1226000000</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
-      <c r="F42">
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>0</v>
       </c>
     </row>
@@ -3784,15 +4691,18 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B43">
-        <v>7207263000</v>
+        <v>8758937000</v>
       </c>
       <c r="C43">
+        <v>7206937000</v>
+      </c>
+      <c r="D43">
         <v>5655937000</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>4036122000</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>668455000</v>
       </c>
     </row>
@@ -3801,15 +4711,18 @@
         <v xml:space="preserve">    DÖNEM NET KARI VEYA ZARARI</v>
       </c>
       <c r="B44">
-        <v>7207263000</v>
+        <v>8758937000</v>
       </c>
       <c r="C44">
+        <v>7206937000</v>
+      </c>
+      <c r="D44">
         <v>5655937000</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>4036122000</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>668455000</v>
       </c>
     </row>
@@ -3818,15 +4731,18 @@
         <v xml:space="preserve">    Grubun Karı (Zararı)</v>
       </c>
       <c r="B45">
-        <v>7207263000</v>
+        <v>8758937000</v>
       </c>
       <c r="C45">
+        <v>7206937000</v>
+      </c>
+      <c r="D45">
         <v>5655937000</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>4036122000</v>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>668455000</v>
       </c>
     </row>
@@ -3843,13 +4759,16 @@
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="F46">
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
   </ignoredErrors>
 </worksheet>
 </file>
